--- a/data/trans_dic/IP31KM15_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,36; 66,56</t>
+          <t>39,44; 58,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,31; 57,1</t>
+          <t>49,92; 69,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,2; 58,46</t>
+          <t>46,64; 61,55</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 40,55</t>
+          <t>24,28; 43,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,68; 43,57</t>
+          <t>29,06; 46,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,82; 38,75</t>
+          <t>29,57; 41,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,45; 59,26</t>
+          <t>29,18; 49,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,71; 49,83</t>
+          <t>37,89; 59,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,68; 50,35</t>
+          <t>36,71; 51,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,76; 79,1</t>
+          <t>52,36; 80,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,35; 81,54</t>
+          <t>61,31; 80,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,57; 77,21</t>
+          <t>60,71; 77,58</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,68; 98,45</t>
+          <t>78,05; 95,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,88; 95,71</t>
+          <t>87,5; 98,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,1; 95,87</t>
+          <t>85,89; 95,69</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,64; 40,24</t>
+          <t>20,79; 40,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,14; 40,95</t>
+          <t>17,2; 37,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,68; 36,65</t>
+          <t>22,18; 36,33</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>67,73; 83,08</t>
+          <t>68,6; 80,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,82; 80,57</t>
+          <t>68,28; 82,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,39; 79,69</t>
+          <t>71,1; 80,22</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,81; 61,05</t>
+          <t>48,85; 63,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,48; 63,33</t>
+          <t>46,28; 61,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50,21; 60,25</t>
+          <t>50,32; 61,3</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47,69; 59,45</t>
+          <t>51,94; 59,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50,79; 57,96</t>
+          <t>54,64; 61,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,2; 57,72</t>
+          <t>54,21; 59,51</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74048</t>
+          <t>62418</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28814; 47525</t>
+          <t>23766; 35510</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27088; 42602</t>
+          <t>27416; 38217</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60152; 85357</t>
+          <t>53718; 70900</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42533</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>75869</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14822; 50949</t>
+          <t>27911; 50038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31203; 55084</t>
+          <t>28863; 45999</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52476; 97677</t>
+          <t>63371; 88489</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24767</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>48294</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21917; 32918</t>
+          <t>16719; 28393</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18558; 32206</t>
+          <t>20503; 32121</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44084; 60510</t>
+          <t>40894; 56821</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>49572</t>
+          <t>46351</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>96780</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41641; 55117</t>
+          <t>36553; 56146</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40209; 61455</t>
+          <t>43201; 56701</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86400; 111995</t>
+          <t>85165; 108823</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32544</t>
+          <t>35336</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69030</t>
+          <t>69040</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29644; 33670</t>
+          <t>30893; 37664</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32528; 38972</t>
+          <t>30950; 34832</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64504; 71822</t>
+          <t>64371; 71721</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>26593</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8254; 17824</t>
+          <t>9813; 18957</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11369; 22022</t>
+          <t>7616; 16788</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21263; 35941</t>
+          <t>20297; 33238</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>136</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>94247</t>
+          <t>105247</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>113929</t>
+          <t>93182</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208175</t>
+          <t>198430</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>83774; 102772</t>
+          <t>96438; 113829</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>97399; 124911</t>
+          <t>83183; 100329</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>190623; 222127</t>
+          <t>186556; 210484</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>96</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>69315</t>
+          <t>88822</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>86782</t>
+          <t>74308</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>156097</t>
+          <t>163130</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>60226; 78553</t>
+          <t>76767; 99618</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>74738; 97636</t>
+          <t>63826; 84358</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>141991; 170399</t>
+          <t>148465; 180859</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>535</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>361860</t>
+          <t>380108</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>360446</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>767453</t>
+          <t>740553</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>311478; 388284</t>
+          <t>356711; 407480</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>378260; 431631</t>
+          <t>337793; 380812</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>715739; 806798</t>
+          <t>707394; 776670</t>
         </is>
       </c>
     </row>
